--- a/artfynd/A 59983-2024 artfynd.xlsx
+++ b/artfynd/A 59983-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127078547</v>
+        <v>127081229</v>
       </c>
       <c r="B2" t="n">
-        <v>56849</v>
+        <v>57654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,31 +708,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>S Borrberget vid Mångån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475625</v>
+        <v>475656</v>
       </c>
       <c r="R2" t="n">
-        <v>6744339</v>
+        <v>6744328</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -788,32 +784,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127081229</v>
+        <v>127078547</v>
       </c>
       <c r="B3" t="n">
-        <v>57654</v>
+        <v>56849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -821,27 +817,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>S Borrberget vid Mångån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475656</v>
+        <v>475625</v>
       </c>
       <c r="R3" t="n">
-        <v>6744328</v>
+        <v>6744339</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>127078602</v>
       </c>
       <c r="B7" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>127081257</v>
       </c>
       <c r="B10" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>127081565</v>
       </c>
       <c r="B11" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>127078662</v>
       </c>
       <c r="B13" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>127078506</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>127081757</v>
       </c>
       <c r="B15" t="n">
-        <v>92537</v>
+        <v>92611</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>127078639</v>
       </c>
       <c r="B17" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 59983-2024 artfynd.xlsx
+++ b/artfynd/A 59983-2024 artfynd.xlsx
@@ -784,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127078547</v>
+        <v>127088204</v>
       </c>
       <c r="B3" t="n">
-        <v>56849</v>
+        <v>5196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,53 +795,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>S Borrberget vid Mångån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475625</v>
+        <v>475658</v>
       </c>
       <c r="R3" t="n">
-        <v>6744339</v>
+        <v>6744302</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,12 +862,18 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flera platser i södra delen av området</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -890,17 +885,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127088204</v>
+        <v>127078547</v>
       </c>
       <c r="B4" t="n">
-        <v>5196</v>
+        <v>56849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,42 +903,53 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>S Borrberget vid Mångån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475658</v>
+        <v>475625</v>
       </c>
       <c r="R4" t="n">
-        <v>6744302</v>
+        <v>6744339</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,18 +981,12 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flera platser i södra delen av området</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -998,7 +998,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1231,7 +1231,7 @@
         <v>127078602</v>
       </c>
       <c r="B7" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>127081257</v>
       </c>
       <c r="B10" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,50 +1679,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127081565</v>
+        <v>127081704</v>
       </c>
       <c r="B11" t="n">
-        <v>98436</v>
+        <v>57654</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1730,13 +1726,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475613</v>
+        <v>475580</v>
       </c>
       <c r="R11" t="n">
-        <v>6744279</v>
+        <v>6744315</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1768,13 +1764,17 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>flera hack på flera träd</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1786,53 +1786,57 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127081704</v>
+        <v>127081565</v>
       </c>
       <c r="B12" t="n">
-        <v>57654</v>
+        <v>98442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1840,13 +1844,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475580</v>
+        <v>475613</v>
       </c>
       <c r="R12" t="n">
-        <v>6744315</v>
+        <v>6744279</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1878,17 +1882,13 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>flera hack på flera träd</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1910,7 +1910,7 @@
         <v>127078662</v>
       </c>
       <c r="B13" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>127078506</v>
       </c>
       <c r="B14" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>127081757</v>
       </c>
       <c r="B15" t="n">
-        <v>92611</v>
+        <v>92617</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>127078639</v>
       </c>
       <c r="B17" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 59983-2024 artfynd.xlsx
+++ b/artfynd/A 59983-2024 artfynd.xlsx
@@ -784,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127088204</v>
+        <v>127078547</v>
       </c>
       <c r="B3" t="n">
-        <v>5196</v>
+        <v>56849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,42 +795,53 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>S Borrberget vid Mångån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475658</v>
+        <v>475625</v>
       </c>
       <c r="R3" t="n">
-        <v>6744302</v>
+        <v>6744339</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,18 +873,12 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flera platser i södra delen av området</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -885,17 +890,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127078547</v>
+        <v>127088204</v>
       </c>
       <c r="B4" t="n">
-        <v>56849</v>
+        <v>5196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,53 +908,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>S Borrberget vid Mångån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475625</v>
+        <v>475658</v>
       </c>
       <c r="R4" t="n">
-        <v>6744339</v>
+        <v>6744302</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,12 +975,18 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flera platser i södra delen av området</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -998,7 +998,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 59983-2024 artfynd.xlsx
+++ b/artfynd/A 59983-2024 artfynd.xlsx
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127081681</v>
+        <v>127081521</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1042,7 +1042,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475608</v>
+        <v>475659</v>
       </c>
       <c r="R5" t="n">
-        <v>6744267</v>
+        <v>6744309</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,17 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhackad gran långt upp på stammen</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,39 +1107,39 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127081521</v>
+        <v>127078602</v>
       </c>
       <c r="B6" t="n">
-        <v>57817</v>
+        <v>98442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1152,13 +1147,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1166,13 +1165,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475659</v>
+        <v>475625</v>
       </c>
       <c r="R6" t="n">
-        <v>6744309</v>
+        <v>6744344</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,12 +1195,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,6 +1209,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1221,39 +1221,39 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson</t>
+          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127078602</v>
+        <v>127081681</v>
       </c>
       <c r="B7" t="n">
-        <v>98442</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1261,17 +1261,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1279,13 +1275,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475625</v>
+        <v>475608</v>
       </c>
       <c r="R7" t="n">
-        <v>6744344</v>
+        <v>6744267</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,13 +1313,17 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhackad gran långt upp på stammen</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1679,46 +1679,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127081704</v>
+        <v>127081565</v>
       </c>
       <c r="B11" t="n">
-        <v>57654</v>
+        <v>98442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1726,13 +1730,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475580</v>
+        <v>475613</v>
       </c>
       <c r="R11" t="n">
-        <v>6744315</v>
+        <v>6744279</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1764,17 +1768,13 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>flera hack på flera träd</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1786,57 +1786,53 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127081565</v>
+        <v>127081704</v>
       </c>
       <c r="B12" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1844,13 +1840,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475613</v>
+        <v>475580</v>
       </c>
       <c r="R12" t="n">
-        <v>6744279</v>
+        <v>6744315</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1882,13 +1878,17 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>flera hack på flera träd</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 59983-2024 artfynd.xlsx
+++ b/artfynd/A 59983-2024 artfynd.xlsx
@@ -784,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127078547</v>
+        <v>127088204</v>
       </c>
       <c r="B3" t="n">
-        <v>56849</v>
+        <v>5196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,53 +795,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>S Borrberget vid Mångån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475625</v>
+        <v>475658</v>
       </c>
       <c r="R3" t="n">
-        <v>6744339</v>
+        <v>6744302</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,12 +862,18 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flera platser i södra delen av området</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -890,17 +885,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127088204</v>
+        <v>127078547</v>
       </c>
       <c r="B4" t="n">
-        <v>5196</v>
+        <v>56849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,42 +903,53 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>S Borrberget vid Mångån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475658</v>
+        <v>475625</v>
       </c>
       <c r="R4" t="n">
-        <v>6744302</v>
+        <v>6744339</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,18 +981,12 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flera platser i södra delen av området</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -998,17 +998,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127081521</v>
+        <v>127081681</v>
       </c>
       <c r="B5" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1042,7 +1042,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475659</v>
+        <v>475608</v>
       </c>
       <c r="R5" t="n">
-        <v>6744309</v>
+        <v>6744267</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,12 +1082,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhackad gran långt upp på stammen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,39 +1112,39 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127078602</v>
+        <v>127081521</v>
       </c>
       <c r="B6" t="n">
-        <v>98442</v>
+        <v>57817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1147,17 +1152,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1165,13 +1166,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475625</v>
+        <v>475659</v>
       </c>
       <c r="R6" t="n">
-        <v>6744344</v>
+        <v>6744309</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1195,12 +1196,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,7 +1210,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1221,39 +1221,39 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Siv Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127081681</v>
+        <v>127078602</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1261,13 +1261,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1275,13 +1279,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475608</v>
+        <v>475625</v>
       </c>
       <c r="R7" t="n">
-        <v>6744267</v>
+        <v>6744344</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1313,17 +1317,13 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhackad gran långt upp på stammen</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1568,7 +1568,7 @@
         <v>127081257</v>
       </c>
       <c r="B10" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,50 +1679,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127081565</v>
+        <v>127081704</v>
       </c>
       <c r="B11" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1730,13 +1726,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475613</v>
+        <v>475580</v>
       </c>
       <c r="R11" t="n">
-        <v>6744279</v>
+        <v>6744315</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1768,13 +1764,17 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>flera hack på flera träd</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1786,53 +1786,57 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127081704</v>
+        <v>127081565</v>
       </c>
       <c r="B12" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1840,13 +1844,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475580</v>
+        <v>475613</v>
       </c>
       <c r="R12" t="n">
-        <v>6744315</v>
+        <v>6744279</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1878,17 +1882,13 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>flera hack på flera träd</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1910,7 +1910,7 @@
         <v>127078662</v>
       </c>
       <c r="B13" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>127078506</v>
       </c>
       <c r="B14" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>127081757</v>
       </c>
       <c r="B15" t="n">
-        <v>92617</v>
+        <v>92618</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>127078639</v>
       </c>
       <c r="B17" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 59983-2024 artfynd.xlsx
+++ b/artfynd/A 59983-2024 artfynd.xlsx
@@ -1119,32 +1119,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127081521</v>
+        <v>127078602</v>
       </c>
       <c r="B6" t="n">
-        <v>57817</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1152,13 +1152,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1166,13 +1170,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475659</v>
+        <v>475625</v>
       </c>
       <c r="R6" t="n">
-        <v>6744309</v>
+        <v>6744344</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,12 +1200,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,6 +1214,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1221,39 +1226,39 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson</t>
+          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127078602</v>
+        <v>127081521</v>
       </c>
       <c r="B7" t="n">
-        <v>98443</v>
+        <v>57817</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1261,17 +1266,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1279,13 +1280,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475625</v>
+        <v>475659</v>
       </c>
       <c r="R7" t="n">
-        <v>6744344</v>
+        <v>6744309</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,12 +1310,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,7 +1324,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Siv Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1679,46 +1679,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127081704</v>
+        <v>127081565</v>
       </c>
       <c r="B11" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1726,13 +1730,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475580</v>
+        <v>475613</v>
       </c>
       <c r="R11" t="n">
-        <v>6744315</v>
+        <v>6744279</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1764,17 +1768,13 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>flera hack på flera träd</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1786,57 +1786,53 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127081565</v>
+        <v>127081704</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>57654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1844,13 +1840,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475613</v>
+        <v>475580</v>
       </c>
       <c r="R12" t="n">
-        <v>6744279</v>
+        <v>6744315</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1882,13 +1878,17 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>flera hack på flera träd</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 59983-2024 artfynd.xlsx
+++ b/artfynd/A 59983-2024 artfynd.xlsx
@@ -1119,32 +1119,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127078602</v>
+        <v>127081521</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>57817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1152,17 +1152,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1170,13 +1166,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475625</v>
+        <v>475659</v>
       </c>
       <c r="R6" t="n">
-        <v>6744344</v>
+        <v>6744309</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,12 +1196,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,7 +1210,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1226,39 +1221,39 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Siv Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127081521</v>
+        <v>127078602</v>
       </c>
       <c r="B7" t="n">
-        <v>57817</v>
+        <v>98443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1266,13 +1261,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1280,13 +1279,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475659</v>
+        <v>475625</v>
       </c>
       <c r="R7" t="n">
-        <v>6744309</v>
+        <v>6744344</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,12 +1309,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,6 +1323,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson</t>
+          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1679,50 +1679,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127081565</v>
+        <v>127081704</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>57654</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1730,13 +1726,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475613</v>
+        <v>475580</v>
       </c>
       <c r="R11" t="n">
-        <v>6744279</v>
+        <v>6744315</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1768,13 +1764,17 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>flera hack på flera träd</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1786,53 +1786,57 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127081704</v>
+        <v>127081565</v>
       </c>
       <c r="B12" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1840,13 +1844,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475580</v>
+        <v>475613</v>
       </c>
       <c r="R12" t="n">
-        <v>6744315</v>
+        <v>6744279</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1878,17 +1882,13 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>flera hack på flera träd</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 59983-2024 artfynd.xlsx
+++ b/artfynd/A 59983-2024 artfynd.xlsx
@@ -1679,46 +1679,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127081704</v>
+        <v>127081565</v>
       </c>
       <c r="B11" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1726,13 +1730,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475580</v>
+        <v>475613</v>
       </c>
       <c r="R11" t="n">
-        <v>6744315</v>
+        <v>6744279</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1764,17 +1768,13 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>flera hack på flera träd</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1786,57 +1786,53 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127081565</v>
+        <v>127081704</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>57654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1844,13 +1840,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475613</v>
+        <v>475580</v>
       </c>
       <c r="R12" t="n">
-        <v>6744279</v>
+        <v>6744315</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1882,13 +1878,17 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>flera hack på flera träd</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 59983-2024 artfynd.xlsx
+++ b/artfynd/A 59983-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127081229</v>
       </c>
       <c r="B2" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127078547</v>
+        <v>127088204</v>
       </c>
       <c r="B3" t="n">
-        <v>56849</v>
+        <v>5197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,53 +795,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>S Borrberget vid Mångån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475625</v>
+        <v>475658</v>
       </c>
       <c r="R3" t="n">
-        <v>6744339</v>
+        <v>6744302</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,12 +862,18 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flera platser i södra delen av området</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -890,17 +885,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127088204</v>
+        <v>127078547</v>
       </c>
       <c r="B4" t="n">
-        <v>5196</v>
+        <v>56853</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,42 +903,53 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>S Borrberget vid Mångån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475658</v>
+        <v>475625</v>
       </c>
       <c r="R4" t="n">
-        <v>6744302</v>
+        <v>6744339</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,18 +981,12 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flera platser i södra delen av området</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -998,7 +998,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
         <v>127081681</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>127081521</v>
       </c>
       <c r="B6" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>127078602</v>
       </c>
       <c r="B7" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>127081647</v>
       </c>
       <c r="B8" t="n">
-        <v>56840</v>
+        <v>56844</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>127081313</v>
       </c>
       <c r="B9" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>127081257</v>
       </c>
       <c r="B10" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,50 +1679,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127081565</v>
+        <v>127081704</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>57658</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1730,13 +1726,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475613</v>
+        <v>475580</v>
       </c>
       <c r="R11" t="n">
-        <v>6744279</v>
+        <v>6744315</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1768,13 +1764,17 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>flera hack på flera träd</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1786,53 +1786,57 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127081704</v>
+        <v>127081565</v>
       </c>
       <c r="B12" t="n">
-        <v>57654</v>
+        <v>98447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1840,13 +1844,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475580</v>
+        <v>475613</v>
       </c>
       <c r="R12" t="n">
-        <v>6744315</v>
+        <v>6744279</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1878,17 +1882,13 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>flera hack på flera träd</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1910,7 +1910,7 @@
         <v>127078662</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>127078506</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>127081757</v>
       </c>
       <c r="B15" t="n">
-        <v>92618</v>
+        <v>92622</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>127081125</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>127078639</v>
       </c>
       <c r="B17" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 59983-2024 artfynd.xlsx
+++ b/artfynd/A 59983-2024 artfynd.xlsx
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127081229</v>
+        <v>127088204</v>
       </c>
       <c r="B2" t="n">
-        <v>57658</v>
+        <v>5197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,18 +703,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475656</v>
+        <v>475658</v>
       </c>
       <c r="R2" t="n">
-        <v>6744328</v>
+        <v>6744302</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,12 +753,18 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flera platser i södra delen av området</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,34 +776,34 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127088204</v>
+        <v>127081229</v>
       </c>
       <c r="B3" t="n">
-        <v>5197</v>
+        <v>57658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -812,11 +811,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475658</v>
+        <v>475656</v>
       </c>
       <c r="R3" t="n">
-        <v>6744302</v>
+        <v>6744328</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,18 +868,12 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flera platser i södra delen av området</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -885,7 +885,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1679,46 +1679,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127081704</v>
+        <v>127081565</v>
       </c>
       <c r="B11" t="n">
-        <v>57658</v>
+        <v>98447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1726,13 +1730,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475580</v>
+        <v>475613</v>
       </c>
       <c r="R11" t="n">
-        <v>6744315</v>
+        <v>6744279</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1764,17 +1768,13 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>flera hack på flera träd</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1786,57 +1786,53 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127081565</v>
+        <v>127081704</v>
       </c>
       <c r="B12" t="n">
-        <v>98447</v>
+        <v>57658</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1844,13 +1840,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475613</v>
+        <v>475580</v>
       </c>
       <c r="R12" t="n">
-        <v>6744279</v>
+        <v>6744315</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1882,13 +1878,17 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>flera hack på flera träd</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 59983-2024 artfynd.xlsx
+++ b/artfynd/A 59983-2024 artfynd.xlsx
@@ -1679,50 +1679,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127081565</v>
+        <v>127081704</v>
       </c>
       <c r="B11" t="n">
-        <v>98447</v>
+        <v>57658</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1730,13 +1726,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475613</v>
+        <v>475580</v>
       </c>
       <c r="R11" t="n">
-        <v>6744279</v>
+        <v>6744315</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1768,13 +1764,17 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>flera hack på flera träd</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1786,53 +1786,57 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127081704</v>
+        <v>127081565</v>
       </c>
       <c r="B12" t="n">
-        <v>57658</v>
+        <v>98447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1840,13 +1844,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475580</v>
+        <v>475613</v>
       </c>
       <c r="R12" t="n">
-        <v>6744315</v>
+        <v>6744279</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1878,17 +1882,13 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>flera hack på flera träd</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 59983-2024 artfynd.xlsx
+++ b/artfynd/A 59983-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127088204</v>
+        <v>127078547</v>
       </c>
       <c r="B2" t="n">
-        <v>5197</v>
+        <v>56853</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,53 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>S Borrberget vid Mångån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475658</v>
+        <v>475625</v>
       </c>
       <c r="R2" t="n">
-        <v>6744302</v>
+        <v>6744339</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,18 +764,12 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flera platser i södra delen av området</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,34 +781,34 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127081229</v>
+        <v>127088204</v>
       </c>
       <c r="B3" t="n">
-        <v>57658</v>
+        <v>5197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -811,18 +816,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,13 +828,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475656</v>
+        <v>475658</v>
       </c>
       <c r="R3" t="n">
-        <v>6744328</v>
+        <v>6744302</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,12 +866,18 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flera platser i södra delen av området</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -885,39 +889,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127078547</v>
+        <v>127081229</v>
       </c>
       <c r="B4" t="n">
-        <v>56853</v>
+        <v>57658</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -925,31 +929,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>S Borrberget vid Mångån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475625</v>
+        <v>475656</v>
       </c>
       <c r="R4" t="n">
-        <v>6744339</v>
+        <v>6744328</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 59983-2024 artfynd.xlsx
+++ b/artfynd/A 59983-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127078547</v>
+        <v>127081229</v>
       </c>
       <c r="B2" t="n">
-        <v>56853</v>
+        <v>57658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,31 +708,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>S Borrberget vid Mångån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475625</v>
+        <v>475656</v>
       </c>
       <c r="R2" t="n">
-        <v>6744339</v>
+        <v>6744328</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -896,32 +892,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127081229</v>
+        <v>127078547</v>
       </c>
       <c r="B4" t="n">
-        <v>57658</v>
+        <v>56853</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -929,27 +925,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>S Borrberget vid Mångån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475656</v>
+        <v>475625</v>
       </c>
       <c r="R4" t="n">
-        <v>6744328</v>
+        <v>6744339</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>127078602</v>
       </c>
       <c r="B7" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>127081257</v>
       </c>
       <c r="B10" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,46 +1679,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127081704</v>
+        <v>127081565</v>
       </c>
       <c r="B11" t="n">
-        <v>57658</v>
+        <v>98448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1726,13 +1730,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475580</v>
+        <v>475613</v>
       </c>
       <c r="R11" t="n">
-        <v>6744315</v>
+        <v>6744279</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1764,17 +1768,13 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>flera hack på flera träd</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1786,57 +1786,53 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127081565</v>
+        <v>127081704</v>
       </c>
       <c r="B12" t="n">
-        <v>98447</v>
+        <v>57658</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1844,13 +1840,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475613</v>
+        <v>475580</v>
       </c>
       <c r="R12" t="n">
-        <v>6744279</v>
+        <v>6744315</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1882,13 +1878,17 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>flera hack på flera träd</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1910,7 +1910,7 @@
         <v>127078662</v>
       </c>
       <c r="B13" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>127078506</v>
       </c>
       <c r="B14" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>127078639</v>
       </c>
       <c r="B17" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 59983-2024 artfynd.xlsx
+++ b/artfynd/A 59983-2024 artfynd.xlsx
@@ -784,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127088204</v>
+        <v>127078547</v>
       </c>
       <c r="B3" t="n">
-        <v>5197</v>
+        <v>56853</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,42 +795,53 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>S Borrberget vid Mångån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475658</v>
+        <v>475625</v>
       </c>
       <c r="R3" t="n">
-        <v>6744302</v>
+        <v>6744339</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,18 +873,12 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flera platser i södra delen av området</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -885,17 +890,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127078547</v>
+        <v>127088204</v>
       </c>
       <c r="B4" t="n">
-        <v>56853</v>
+        <v>5197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,53 +908,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>S Borrberget vid Mångån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475625</v>
+        <v>475658</v>
       </c>
       <c r="R4" t="n">
-        <v>6744339</v>
+        <v>6744302</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,12 +975,18 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flera platser i södra delen av området</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -998,7 +998,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1679,50 +1679,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127081565</v>
+        <v>127081704</v>
       </c>
       <c r="B11" t="n">
-        <v>98448</v>
+        <v>57658</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1730,13 +1726,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475613</v>
+        <v>475580</v>
       </c>
       <c r="R11" t="n">
-        <v>6744279</v>
+        <v>6744315</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1768,13 +1764,17 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>flera hack på flera träd</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1786,53 +1786,57 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127081704</v>
+        <v>127081565</v>
       </c>
       <c r="B12" t="n">
-        <v>57658</v>
+        <v>98448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1840,13 +1844,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475580</v>
+        <v>475613</v>
       </c>
       <c r="R12" t="n">
-        <v>6744315</v>
+        <v>6744279</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1878,17 +1882,13 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>flera hack på flera träd</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 59983-2024 artfynd.xlsx
+++ b/artfynd/A 59983-2024 artfynd.xlsx
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127081229</v>
+        <v>127088204</v>
       </c>
       <c r="B2" t="n">
-        <v>57658</v>
+        <v>5197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,18 +703,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475656</v>
+        <v>475658</v>
       </c>
       <c r="R2" t="n">
-        <v>6744328</v>
+        <v>6744302</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,12 +753,18 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flera platser i södra delen av området</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,7 +776,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -787,7 +786,7 @@
         <v>127078547</v>
       </c>
       <c r="B3" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,27 +896,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127088204</v>
+        <v>127081229</v>
       </c>
       <c r="B4" t="n">
-        <v>5197</v>
+        <v>57660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -925,11 +924,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -937,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475658</v>
+        <v>475656</v>
       </c>
       <c r="R4" t="n">
-        <v>6744302</v>
+        <v>6744328</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,18 +981,12 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flera platser i södra delen av området</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -998,7 +998,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
         <v>127081681</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>127081521</v>
       </c>
       <c r="B6" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>127078602</v>
       </c>
       <c r="B7" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>127081647</v>
       </c>
       <c r="B8" t="n">
-        <v>56844</v>
+        <v>56846</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>127081313</v>
       </c>
       <c r="B9" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>127081257</v>
       </c>
       <c r="B10" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,46 +1679,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127081704</v>
+        <v>127081565</v>
       </c>
       <c r="B11" t="n">
-        <v>57658</v>
+        <v>98450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1726,13 +1730,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475580</v>
+        <v>475613</v>
       </c>
       <c r="R11" t="n">
-        <v>6744315</v>
+        <v>6744279</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1764,17 +1768,13 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>flera hack på flera träd</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1786,57 +1786,53 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127081565</v>
+        <v>127081704</v>
       </c>
       <c r="B12" t="n">
-        <v>98448</v>
+        <v>57660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1844,13 +1840,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475613</v>
+        <v>475580</v>
       </c>
       <c r="R12" t="n">
-        <v>6744279</v>
+        <v>6744315</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1882,13 +1878,17 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>flera hack på flera träd</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1910,7 +1910,7 @@
         <v>127078662</v>
       </c>
       <c r="B13" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>127078506</v>
       </c>
       <c r="B14" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>127081757</v>
       </c>
       <c r="B15" t="n">
-        <v>92622</v>
+        <v>92624</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>127081125</v>
       </c>
       <c r="B16" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>127078639</v>
       </c>
       <c r="B17" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 59983-2024 artfynd.xlsx
+++ b/artfynd/A 59983-2024 artfynd.xlsx
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127088204</v>
+        <v>127081229</v>
       </c>
       <c r="B2" t="n">
-        <v>5197</v>
+        <v>57660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,11 +703,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -715,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475658</v>
+        <v>475656</v>
       </c>
       <c r="R2" t="n">
-        <v>6744302</v>
+        <v>6744328</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,18 +760,12 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flera platser i södra delen av området</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,17 +777,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127078547</v>
+        <v>127088204</v>
       </c>
       <c r="B3" t="n">
-        <v>56855</v>
+        <v>5197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -794,53 +795,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>S Borrberget vid Mångån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475625</v>
+        <v>475658</v>
       </c>
       <c r="R3" t="n">
-        <v>6744339</v>
+        <v>6744302</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,12 +862,18 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flera platser i södra delen av området</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,39 +885,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127081229</v>
+        <v>127078547</v>
       </c>
       <c r="B4" t="n">
-        <v>57660</v>
+        <v>56855</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -929,27 +925,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>S Borrberget vid Mångån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475656</v>
+        <v>475625</v>
       </c>
       <c r="R4" t="n">
-        <v>6744328</v>
+        <v>6744339</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
+          <t>Birgitta Kvist, Siv Andersson , Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 59983-2024 artfynd.xlsx
+++ b/artfynd/A 59983-2024 artfynd.xlsx
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127081681</v>
+        <v>127081521</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1042,7 +1042,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475608</v>
+        <v>475659</v>
       </c>
       <c r="R5" t="n">
-        <v>6744267</v>
+        <v>6744309</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,17 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhackad gran långt upp på stammen</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,39 +1107,39 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127081521</v>
+        <v>127078602</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>98450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1152,13 +1147,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1166,13 +1165,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475659</v>
+        <v>475625</v>
       </c>
       <c r="R6" t="n">
-        <v>6744309</v>
+        <v>6744344</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,12 +1195,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,6 +1209,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1221,39 +1221,39 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson</t>
+          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127078602</v>
+        <v>127081681</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1261,17 +1261,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1279,13 +1275,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475625</v>
+        <v>475608</v>
       </c>
       <c r="R7" t="n">
-        <v>6744344</v>
+        <v>6744267</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,13 +1313,17 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhackad gran långt upp på stammen</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1679,50 +1679,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127081565</v>
+        <v>127081704</v>
       </c>
       <c r="B11" t="n">
-        <v>98450</v>
+        <v>57660</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1730,13 +1726,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475613</v>
+        <v>475580</v>
       </c>
       <c r="R11" t="n">
-        <v>6744279</v>
+        <v>6744315</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1768,13 +1764,17 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>flera hack på flera träd</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1786,53 +1786,57 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127081704</v>
+        <v>127081565</v>
       </c>
       <c r="B12" t="n">
-        <v>57660</v>
+        <v>98450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1840,13 +1844,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475580</v>
+        <v>475613</v>
       </c>
       <c r="R12" t="n">
-        <v>6744315</v>
+        <v>6744279</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1878,17 +1882,13 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>flera hack på flera träd</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 59983-2024 artfynd.xlsx
+++ b/artfynd/A 59983-2024 artfynd.xlsx
@@ -784,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127088204</v>
+        <v>127078547</v>
       </c>
       <c r="B3" t="n">
-        <v>5197</v>
+        <v>56855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,42 +795,53 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>S Borrberget vid Mångån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475658</v>
+        <v>475625</v>
       </c>
       <c r="R3" t="n">
-        <v>6744302</v>
+        <v>6744339</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,18 +873,12 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flera platser i södra delen av området</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -885,17 +890,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127078547</v>
+        <v>127088204</v>
       </c>
       <c r="B4" t="n">
-        <v>56855</v>
+        <v>5197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,53 +908,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>S Borrberget vid Mångån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475625</v>
+        <v>475658</v>
       </c>
       <c r="R4" t="n">
-        <v>6744339</v>
+        <v>6744302</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,12 +975,18 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flera platser i södra delen av området</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -998,17 +998,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127081521</v>
+        <v>127081681</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1042,7 +1042,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475659</v>
+        <v>475608</v>
       </c>
       <c r="R5" t="n">
-        <v>6744309</v>
+        <v>6744267</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,12 +1082,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhackad gran långt upp på stammen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,39 +1112,39 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127078602</v>
+        <v>127081521</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1147,17 +1152,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1165,13 +1166,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475625</v>
+        <v>475659</v>
       </c>
       <c r="R6" t="n">
-        <v>6744344</v>
+        <v>6744309</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1195,12 +1196,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,7 +1210,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1221,39 +1221,39 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
+          <t>Siv Andersson , Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127081681</v>
+        <v>127078602</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>98450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1261,13 +1261,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1275,13 +1279,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475608</v>
+        <v>475625</v>
       </c>
       <c r="R7" t="n">
-        <v>6744267</v>
+        <v>6744344</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1313,17 +1317,13 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhackad gran långt upp på stammen</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson</t>
+          <t>Siv Andersson , Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Siv Andersson , Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 59983-2024 artfynd.xlsx
+++ b/artfynd/A 59983-2024 artfynd.xlsx
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127081229</v>
+        <v>127088204</v>
       </c>
       <c r="B2" t="n">
-        <v>57660</v>
+        <v>5197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,18 +703,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475656</v>
+        <v>475658</v>
       </c>
       <c r="R2" t="n">
-        <v>6744328</v>
+        <v>6744302</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,12 +753,18 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flera platser i södra delen av området</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,39 +776,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127078547</v>
+        <v>127081229</v>
       </c>
       <c r="B3" t="n">
-        <v>56855</v>
+        <v>57660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -817,31 +816,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>S Borrberget vid Mångån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475625</v>
+        <v>475656</v>
       </c>
       <c r="R3" t="n">
-        <v>6744339</v>
+        <v>6744328</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127088204</v>
+        <v>127078547</v>
       </c>
       <c r="B4" t="n">
-        <v>5197</v>
+        <v>56855</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,42 +903,53 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>S Borrberget vid Mångån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475658</v>
+        <v>475625</v>
       </c>
       <c r="R4" t="n">
-        <v>6744302</v>
+        <v>6744339</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,18 +981,12 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flera platser i södra delen av området</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -998,17 +998,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127081681</v>
+        <v>127081521</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1042,7 +1042,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475608</v>
+        <v>475659</v>
       </c>
       <c r="R5" t="n">
-        <v>6744267</v>
+        <v>6744309</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,17 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhackad gran långt upp på stammen</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,17 +1107,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127081521</v>
+        <v>127081681</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,21 +1125,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1156,7 +1151,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1166,13 +1161,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475659</v>
+        <v>475608</v>
       </c>
       <c r="R6" t="n">
-        <v>6744309</v>
+        <v>6744267</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,12 +1191,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhackad gran långt upp på stammen</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Siv Andersson , Bengt Oldhammer</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1231,7 +1231,7 @@
         <v>127078602</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>127081257</v>
       </c>
       <c r="B10" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>127081565</v>
       </c>
       <c r="B12" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Siv Andersson , Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1910,7 +1910,7 @@
         <v>127078662</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>127078506</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>127081757</v>
       </c>
       <c r="B15" t="n">
-        <v>92624</v>
+        <v>92630</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>127078639</v>
       </c>
       <c r="B17" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 59983-2024 artfynd.xlsx
+++ b/artfynd/A 59983-2024 artfynd.xlsx
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127088204</v>
+        <v>127081229</v>
       </c>
       <c r="B2" t="n">
-        <v>5197</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,11 +703,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -715,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475658</v>
+        <v>475656</v>
       </c>
       <c r="R2" t="n">
-        <v>6744302</v>
+        <v>6744328</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,18 +760,12 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flera platser i södra delen av området</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,39 +777,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127081229</v>
+        <v>127078547</v>
       </c>
       <c r="B3" t="n">
-        <v>57660</v>
+        <v>56858</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -816,27 +817,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>S Borrberget vid Mångån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475656</v>
+        <v>475625</v>
       </c>
       <c r="R3" t="n">
-        <v>6744328</v>
+        <v>6744339</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127078547</v>
+        <v>127088204</v>
       </c>
       <c r="B4" t="n">
-        <v>56855</v>
+        <v>5197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,53 +908,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>S Borrberget vid Mångån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475625</v>
+        <v>475658</v>
       </c>
       <c r="R4" t="n">
-        <v>6744339</v>
+        <v>6744302</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,12 +975,18 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flera platser i södra delen av området</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -998,7 +998,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson , Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
         <v>127081521</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>127081681</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>127078602</v>
       </c>
       <c r="B7" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>127081647</v>
       </c>
       <c r="B8" t="n">
-        <v>56846</v>
+        <v>56849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>127081313</v>
       </c>
       <c r="B9" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>127081257</v>
       </c>
       <c r="B10" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>127081704</v>
       </c>
       <c r="B11" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>127081565</v>
       </c>
       <c r="B12" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>127078662</v>
       </c>
       <c r="B13" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>127078506</v>
       </c>
       <c r="B14" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>127081757</v>
       </c>
       <c r="B15" t="n">
-        <v>92630</v>
+        <v>92633</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>127081125</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>127078639</v>
       </c>
       <c r="B17" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 59983-2024 artfynd.xlsx
+++ b/artfynd/A 59983-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127081229</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127078547</v>
       </c>
       <c r="B3" t="n">
-        <v>56858</v>
+        <v>56849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>127088204</v>
       </c>
       <c r="B4" t="n">
-        <v>5197</v>
+        <v>5196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127081521</v>
+        <v>127081681</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1042,7 +1042,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475659</v>
+        <v>475608</v>
       </c>
       <c r="R5" t="n">
-        <v>6744309</v>
+        <v>6744267</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,12 +1082,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhackad gran långt upp på stammen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,17 +1112,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127081681</v>
+        <v>127081521</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>57817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1151,7 +1156,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1161,13 +1166,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475608</v>
+        <v>475659</v>
       </c>
       <c r="R6" t="n">
-        <v>6744267</v>
+        <v>6744309</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,17 +1196,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhackad gran långt upp på stammen</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1231,7 +1231,7 @@
         <v>127078602</v>
       </c>
       <c r="B7" t="n">
-        <v>98459</v>
+        <v>98436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>127081647</v>
       </c>
       <c r="B8" t="n">
-        <v>56849</v>
+        <v>56840</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>127081313</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>127081257</v>
       </c>
       <c r="B10" t="n">
-        <v>98459</v>
+        <v>98436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,46 +1679,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127081704</v>
+        <v>127081565</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>98436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1726,13 +1730,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475580</v>
+        <v>475613</v>
       </c>
       <c r="R11" t="n">
-        <v>6744315</v>
+        <v>6744279</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1764,17 +1768,13 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>flera hack på flera träd</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1786,57 +1786,53 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127081565</v>
+        <v>127081704</v>
       </c>
       <c r="B12" t="n">
-        <v>98459</v>
+        <v>57654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1844,13 +1840,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475613</v>
+        <v>475580</v>
       </c>
       <c r="R12" t="n">
-        <v>6744279</v>
+        <v>6744315</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1882,13 +1878,17 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>flera hack på flera träd</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1910,7 +1910,7 @@
         <v>127078662</v>
       </c>
       <c r="B13" t="n">
-        <v>98459</v>
+        <v>98436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>127078506</v>
       </c>
       <c r="B14" t="n">
-        <v>98459</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>127081757</v>
       </c>
       <c r="B15" t="n">
-        <v>92633</v>
+        <v>92611</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>127081125</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>127078639</v>
       </c>
       <c r="B17" t="n">
-        <v>98459</v>
+        <v>98436</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 59983-2024 artfynd.xlsx
+++ b/artfynd/A 59983-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127081229</v>
       </c>
       <c r="B2" t="n">
-        <v>57654</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127078547</v>
       </c>
       <c r="B3" t="n">
-        <v>56849</v>
+        <v>56858</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>127088204</v>
       </c>
       <c r="B4" t="n">
-        <v>5196</v>
+        <v>5197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127081681</v>
+        <v>127081521</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1042,7 +1042,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475608</v>
+        <v>475659</v>
       </c>
       <c r="R5" t="n">
-        <v>6744267</v>
+        <v>6744309</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,17 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhackad gran långt upp på stammen</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,17 +1107,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127081521</v>
+        <v>127081681</v>
       </c>
       <c r="B6" t="n">
-        <v>57817</v>
+        <v>57666</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,21 +1125,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1156,7 +1151,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1166,13 +1161,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475659</v>
+        <v>475608</v>
       </c>
       <c r="R6" t="n">
-        <v>6744309</v>
+        <v>6744267</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,12 +1191,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhackad gran långt upp på stammen</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1231,7 +1231,7 @@
         <v>127078602</v>
       </c>
       <c r="B7" t="n">
-        <v>98436</v>
+        <v>98459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>127081647</v>
       </c>
       <c r="B8" t="n">
-        <v>56840</v>
+        <v>56849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>127081313</v>
       </c>
       <c r="B9" t="n">
-        <v>57654</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>127081257</v>
       </c>
       <c r="B10" t="n">
-        <v>98436</v>
+        <v>98459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,50 +1679,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127081565</v>
+        <v>127081704</v>
       </c>
       <c r="B11" t="n">
-        <v>98436</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1730,13 +1726,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475613</v>
+        <v>475580</v>
       </c>
       <c r="R11" t="n">
-        <v>6744279</v>
+        <v>6744315</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1768,13 +1764,17 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>flera hack på flera träd</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1786,53 +1786,57 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Siv Andersson</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127081704</v>
+        <v>127081565</v>
       </c>
       <c r="B12" t="n">
-        <v>57654</v>
+        <v>98459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1840,13 +1844,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475580</v>
+        <v>475613</v>
       </c>
       <c r="R12" t="n">
-        <v>6744315</v>
+        <v>6744279</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1878,17 +1882,13 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>flera hack på flera träd</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Siv Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1910,7 +1910,7 @@
         <v>127078662</v>
       </c>
       <c r="B13" t="n">
-        <v>98436</v>
+        <v>98459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>127078506</v>
       </c>
       <c r="B14" t="n">
-        <v>98436</v>
+        <v>98459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>127081757</v>
       </c>
       <c r="B15" t="n">
-        <v>92611</v>
+        <v>92633</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>127081125</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>57666</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>127078639</v>
       </c>
       <c r="B17" t="n">
-        <v>98436</v>
+        <v>98459</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
